--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104632_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104632_W20.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.464399999999999</v>
+        <v>9.776300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1228</v>
+        <v>9.9625</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6583</v>
+        <v>-0.1861</v>
       </c>
       <c r="G2" t="n">
-        <v>8.4458</v>
+        <v>8.4336</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2091</v>
+        <v>1.2173</v>
       </c>
       <c r="I2" t="n">
-        <v>7.2367</v>
+        <v>7.2163</v>
       </c>
       <c r="J2" t="n">
-        <v>9.244199999999999</v>
+        <v>9.205299999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7144</v>
+        <v>1.7064</v>
       </c>
       <c r="L2" t="n">
-        <v>7.5299</v>
+        <v>7.4988</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7984</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2594</v>
+        <v>0.0743</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9043</v>
+        <v>-0.0073</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3551</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0513</v>
+        <v>3.3214</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8282</v>
+        <v>3.1105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2231</v>
+        <v>0.2109</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5357</v>
+        <v>0.5421</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3304</v>
+        <v>0.3303</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2053</v>
+        <v>0.2118</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4229</v>
+        <v>1.4127</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3434</v>
+        <v>1.3405</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8871</v>
+        <v>-0.8706</v>
       </c>
       <c r="N3" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5155</v>
+        <v>0.7793</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3126</v>
+        <v>0.6083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2029</v>
+        <v>0.171</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7875</v>
+        <v>1.7775</v>
       </c>
       <c r="E4" t="n">
-        <v>2.477</v>
+        <v>2.0486</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3105</v>
+        <v>-0.2712</v>
       </c>
       <c r="G4" t="n">
-        <v>1.759</v>
+        <v>1.7671</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0531</v>
+        <v>0.0708</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7059</v>
+        <v>1.6962</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5223</v>
+        <v>2.4951</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7793</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7431</v>
+        <v>1.7195</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7634</v>
+        <v>-0.728</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7261</v>
+        <v>-0.7048</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0372</v>
+        <v>-0.0232</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>2.4407</v>
+        <v>1.417</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3157</v>
+        <v>0.9193</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1251</v>
+        <v>0.4977</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. SHERMADINI</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8328</v>
+        <v>1.3836</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4131</v>
+        <v>0.3291</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5804</v>
+        <v>1.0545</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1655</v>
+        <v>0.2345</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9815</v>
+        <v>0.3732</v>
       </c>
       <c r="I5" t="n">
-        <v>0.184</v>
+        <v>-0.1387</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0625</v>
+        <v>0.3315</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8013</v>
+        <v>0.0862</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2612</v>
+        <v>0.2453</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8971</v>
+        <v>-0.097</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8198</v>
+        <v>0.287</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7995</v>
+        <v>0.7817</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5243</v>
+        <v>-0.0024</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2752</v>
+        <v>0.7842</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7712</v>
+        <v>-0.3155</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>G. SHERMADINI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4105</v>
+        <v>0.9445</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2214</v>
+        <v>1.4945</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1891</v>
+        <v>-0.55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2334</v>
+        <v>2.1552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3693</v>
+        <v>1.9627</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.136</v>
+        <v>0.1925</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3424</v>
+        <v>3.0283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0866</v>
+        <v>2.7677</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2558</v>
+        <v>0.2607</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.109</v>
+        <v>-0.8731</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2828</v>
+        <v>-0.805</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3918</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8181</v>
+        <v>0.929</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.121</v>
+        <v>0.6546</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9391</v>
+        <v>0.2744</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3214</v>
+        <v>-0.7739</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>D. BORDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2465</v>
+        <v>-0.0144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9796</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7331</v>
+        <v>-0.0144</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8104</v>
+        <v>-0.0144</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7141999999999999</v>
+        <v>-0.1724</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5247</v>
+        <v>0.1579</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9584</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1878</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2293</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7689</v>
+        <v>-0.0144</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4735</v>
+        <v>-0.1724</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2954</v>
+        <v>0.1579</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.764</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.248</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.516</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BORDON</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0529</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.8411</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0159</v>
+        <v>-0.894</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0159</v>
+        <v>-0.8103</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1732</v>
+        <v>0.7151</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>-1.5254</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.9366</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.1754</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.2388</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0159</v>
+        <v>-1.7469</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1732</v>
+        <v>-0.4603</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>-1.2866</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1321</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.3278</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0195</v>
+        <v>-1.0401</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2851</v>
+        <v>-0.2372</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.8028999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8344</v>
+        <v>0.8379</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0187</v>
+        <v>0.02</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8157</v>
+        <v>0.8179</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7533</v>
+        <v>1.7374</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1141</v>
+        <v>0.1067</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.8995</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3729</v>
+        <v>0.3496</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2299</v>
+        <v>0.3017</v>
       </c>
       <c r="U9" t="n">
-        <v>0.143</v>
+        <v>0.0479</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7925</v>
+        <v>-1.4431</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2636</v>
+        <v>-0.2882</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5289</v>
+        <v>-1.1549</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7117</v>
+        <v>-1.3618</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5465</v>
+        <v>-0.0405</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2582</v>
+        <v>-1.3213</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2415</v>
+        <v>-0.316</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6243</v>
+        <v>0.362</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8658</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5299</v>
+        <v>-1.0458</v>
       </c>
       <c r="N10" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.4025</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6077</v>
+        <v>-0.6433</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.6293</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>0.643</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4567</v>
+        <v>0.0278</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1863</v>
+        <v>-0.0196</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4822</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5748</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8521</v>
+        <v>-1.4676</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.589</v>
+        <v>-1.0874</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2631</v>
+        <v>-0.3802</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3684</v>
+        <v>0.6932</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0463</v>
+        <v>-0.5702</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3221</v>
+        <v>1.2634</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3108</v>
+        <v>1.2059</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3637</v>
+        <v>-0.656</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6744</v>
+        <v>1.8618</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0576</v>
+        <v>-0.5127</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4099</v>
+        <v>0.0857</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.5984</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3911</v>
+        <v>1.008</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2782</v>
+        <v>0.6965</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1128</v>
+        <v>0.3115</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>0.4733</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5628</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8862</v>
+        <v>-3.6075</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0351</v>
+        <v>-3.2267</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8511</v>
+        <v>-0.3808</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6683</v>
+        <v>-3.6608</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6856</v>
+        <v>-0.6755</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9827</v>
+        <v>-2.9853</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2003</v>
+        <v>-3.2194</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3534</v>
+        <v>-0.3587</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.8469</v>
+        <v>-2.8607</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.468</v>
+        <v>-0.4414</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0325</v>
+        <v>0.2323</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6079</v>
+        <v>0.2203</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4246</v>
+        <v>0.0119</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.226800000000001</v>
+        <v>9.577700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>12.8693</v>
+        <v>12.9468</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6425</v>
+        <v>-3.3691</v>
       </c>
       <c r="G13" t="n">
-        <v>8.822500000000002</v>
+        <v>8.8163</v>
       </c>
       <c r="H13" t="n">
-        <v>3.224700000000001</v>
+        <v>3.2308</v>
       </c>
       <c r="I13" t="n">
-        <v>5.597600000000002</v>
+        <v>5.585299999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>17.0364</v>
+        <v>16.8174</v>
       </c>
       <c r="K13" t="n">
-        <v>6.149</v>
+        <v>6.037600000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>10.8878</v>
+        <v>10.78</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.2142</v>
+        <v>-8.001099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.9237</v>
+        <v>-2.8067</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.290400000000001</v>
+        <v>-5.1945</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.402500000000001</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.61</v>
+        <v>-13.6577</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6707</v>
+        <v>6.039300000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1758</v>
+        <v>3.5509</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4951</v>
+        <v>2.4884</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.863800000000001</v>
+        <v>-1.8634</v>
       </c>
       <c r="W13" t="n">
-        <v>6.2669</v>
+        <v>6.2362</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.1309</v>
+        <v>-8.099699999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.562</v>
+        <v>3.6326</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2373</v>
+        <v>4.3851</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3247</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5803</v>
+        <v>4.4641</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2512</v>
+        <v>2.0913</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8316</v>
+        <v>2.3729</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8104</v>
+        <v>6.0531</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6611</v>
+        <v>2.7094</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1493</v>
+        <v>3.3436</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3908</v>
+        <v>-1.589</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4099</v>
+        <v>-0.6182</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7548</v>
+        <v>-1.0592</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1735</v>
+        <v>-0.5298</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5813</v>
+        <v>-0.5294</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0008</v>
+        <v>2.5974</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1854</v>
+        <v>2.6278</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1846</v>
+        <v>-0.0304</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4731</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0982</v>
+        <v>0.2418</v>
       </c>
       <c r="I15" t="n">
-        <v>2.375</v>
+        <v>-0.8218</v>
       </c>
       <c r="J15" t="n">
-        <v>6.0847</v>
+        <v>0.7932</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7289</v>
+        <v>0.6443</v>
       </c>
       <c r="L15" t="n">
-        <v>3.3558</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6116</v>
+        <v>-1.3733</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6308</v>
+        <v>-0.4025</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6991</v>
+        <v>0.7921</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7652</v>
+        <v>0.5874</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9340000000000001</v>
+        <v>0.2047</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3454</v>
+        <v>1.6308</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0403</v>
+        <v>1.2621</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3051</v>
+        <v>0.3687</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3525</v>
+        <v>-0.3417</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1286</v>
+        <v>-0.1183</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2239</v>
+        <v>-0.2234</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7177</v>
+        <v>1.7037</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5619</v>
+        <v>1.5486</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0702</v>
+        <v>-2.0455</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7858</v>
+        <v>-1.772</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6611</v>
+        <v>-0.3948</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6775</v>
+        <v>-0.4416</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0163</v>
+        <v>0.0468</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1904</v>
+        <v>0.4033</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4509</v>
+        <v>3.5559</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6413</v>
+        <v>-3.1527</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.8686</v>
+        <v>3.7177</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0058</v>
+        <v>1.0752</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8628</v>
+        <v>2.6425</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.1079</v>
+        <v>5.4922</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3432</v>
+        <v>1.6645</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.7647</v>
+        <v>3.8277</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7606</v>
+        <v>-1.7745</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6626</v>
+        <v>-0.5893</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0981</v>
+        <v>-1.1852</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4657</v>
+        <v>-0.4542</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1825</v>
+        <v>-0.2047</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2831</v>
+        <v>-0.2494</v>
       </c>
       <c r="V17" t="n">
-        <v>4.917</v>
+        <v>-1.9497</v>
       </c>
       <c r="W17" t="n">
-        <v>6.0097</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.336</v>
+        <v>-0.1351</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1345</v>
+        <v>0.7499</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4705</v>
+        <v>-0.885</v>
       </c>
       <c r="G18" t="n">
-        <v>3.7383</v>
+        <v>-3.8671</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0941</v>
+        <v>-1.0025</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6442</v>
+        <v>-2.8646</v>
       </c>
       <c r="J18" t="n">
-        <v>5.534</v>
+        <v>-2.1363</v>
       </c>
       <c r="K18" t="n">
-        <v>1.693</v>
+        <v>-0.3555</v>
       </c>
       <c r="L18" t="n">
-        <v>3.8409</v>
+        <v>-1.7808</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7957</v>
+        <v>-1.7309</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.599</v>
+        <v>-0.6471</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1967</v>
+        <v>-1.0838</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>2.5039</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2064</v>
+        <v>-1.3982</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6775</v>
+        <v>-0.8296</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.529</v>
+        <v>-0.5686</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.9604</v>
+        <v>4.9026</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>5.9921</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.5068</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8027</v>
+        <v>-2.0849</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.4988</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7945</v>
+        <v>-1.5861</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4825</v>
+        <v>-1.4855</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6722</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8103</v>
+        <v>-0.8026</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3076</v>
+        <v>-0.3267</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4196</v>
+        <v>-0.4384</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1749</v>
+        <v>-1.1588</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3617</v>
+        <v>-0.648</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2994</v>
+        <v>-0.1721</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6611</v>
+        <v>-0.476</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9311</v>
+        <v>-2.6732</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8804</v>
+        <v>-0.8909</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0506</v>
+        <v>-1.7824</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1657</v>
+        <v>-1.1646</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3362</v>
+        <v>-1.3328</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1706</v>
+        <v>0.1682</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3239</v>
+        <v>-0.3332</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8417</v>
+        <v>-0.8314</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9657</v>
+        <v>-0.7166</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5565</v>
+        <v>-0.5576</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4092</v>
+        <v>-0.159</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4467</v>
+        <v>-2.8285</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1473</v>
+        <v>-1.0796</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2994</v>
+        <v>-1.7489</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.7215</v>
+        <v>-3.7585</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8427</v>
+        <v>-2.0829</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8788</v>
+        <v>-1.6757</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.2562</v>
+        <v>-0.8933</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4169</v>
+        <v>-0.6173</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8393</v>
+        <v>-0.276</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4653</v>
+        <v>-2.8653</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4258</v>
+        <v>-1.4656</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0395</v>
+        <v>-1.3997</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.313</v>
+        <v>-0.5936</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1089</v>
+        <v>-0.3441</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4219</v>
+        <v>-0.2494</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7543</v>
+        <v>-3.2871</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5357</v>
+        <v>-3.1683</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2186</v>
+        <v>-0.1188</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7732</v>
+        <v>-4.7237</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0939</v>
+        <v>-1.8411</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6793</v>
+        <v>-2.8826</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8798</v>
+        <v>-3.2794</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6132</v>
+        <v>-1.4242</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2666</v>
+        <v>-1.8553</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8933</v>
+        <v>-1.4442</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4807</v>
+        <v>-0.4169</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4126</v>
+        <v>-1.0273</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5028</v>
+        <v>-0.1568</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8166</v>
+        <v>0.1111</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6863</v>
+        <v>-0.268</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.674</v>
+        <v>-5.6948</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8342</v>
+        <v>-3.5743</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8398</v>
+        <v>-2.1205</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0896</v>
+        <v>-1.0768</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4111</v>
+        <v>0.4216</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5007</v>
+        <v>-1.4985</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9429</v>
+        <v>0.9278</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2468</v>
+        <v>1.2411</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0325</v>
+        <v>-2.0047</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7501</v>
+        <v>-0.2717</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5989</v>
+        <v>-0.1072</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1512</v>
+        <v>-0.1645</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.227000000000004</v>
+        <v>-8.439499999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>3.642599999999997</v>
+        <v>3.368899999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.8695</v>
+        <v>-11.8086</v>
       </c>
       <c r="G24" t="n">
-        <v>-8.822500000000002</v>
+        <v>-8.8162</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.2248</v>
+        <v>-3.230700000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.5976</v>
+        <v>-5.585599999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>8.2143</v>
+        <v>8.001099999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9238</v>
+        <v>2.8066</v>
       </c>
       <c r="L24" t="n">
-        <v>5.2905</v>
+        <v>5.1944</v>
       </c>
       <c r="M24" t="n">
-        <v>-17.0366</v>
+        <v>-16.8176</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.1487</v>
+        <v>-6.0374</v>
       </c>
       <c r="O24" t="n">
-        <v>-10.8877</v>
+        <v>-10.7801</v>
       </c>
       <c r="P24" t="n">
-        <v>3.402500000000001</v>
+        <v>3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-10.2075</v>
+        <v>-10.2434</v>
       </c>
       <c r="R24" t="n">
-        <v>13.6101</v>
+        <v>13.658</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.6706</v>
+        <v>-4.901</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.4951</v>
+        <v>-2.4882</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.175800000000001</v>
+        <v>-2.412799999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8638</v>
+        <v>1.863399999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>8.130800000000001</v>
+        <v>8.099600000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.2671</v>
+        <v>-6.2363</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104632_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104632_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.099699999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104632_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.2363</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
